--- a/SoftwareEngineeringStuff/UtilityTree/UtilityTree.xlsx
+++ b/SoftwareEngineeringStuff/UtilityTree/UtilityTree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DHBW\Semester3\Softwareengineering\caesars-gambit\SoftwareEngineeringStuff\UtilityTree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056ECF47-EACD-401D-BD7B-34E7784020CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0000712-076E-4678-9661-9597D83D8D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5306FDB6-CEE6-4851-9523-6342DEE0678A}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t xml:space="preserve">Echtzeit-Synchronisation zwischenSpielern </t>
   </si>
   <si>
-    <t>Spielzustand wird nach Spielzug in Echtzeit an alle Mitspieler übertragen. Spieler beendet seinen Zug, alle erhalten aktuelle Daten innerhalb von 200 ms. Umgebung: Online-Multiplayer mit 6 Spielern.</t>
-  </si>
-  <si>
     <t>H</t>
   </si>
   <si>
@@ -105,6 +102,9 @@
   </si>
   <si>
     <t>Quality attribute</t>
+  </si>
+  <si>
+    <t>Spielzustand wird nach Spielzug in Echtzeit an alle Mitspieler übertragen. Spieler beendet seinen Zug, alle erhalten aktuelle Daten. Umgebung: Online-Multiplayer mit 6 Spielern.</t>
   </si>
 </sst>
 </file>
@@ -549,7 +549,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -572,80 +572,80 @@
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="1" customFormat="1" ht="68.349999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="57" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="57" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
